--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5611,0.2387,0.1333,0.2098</t>
-  </si>
-  <si>
-    <t>0.0331,0.0032,0.0008,0.9896</t>
-  </si>
-  <si>
-    <t>0.5562,0.0038,0.0094,0.6099</t>
-  </si>
-  <si>
-    <t>0.0464,0.0013,0.0011,0.9895</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0026,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9961,0.0030,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0016,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6609,0.0675,0.3311,0.0096</t>
-  </si>
-  <si>
-    <t>0.3626,0.0147,0.7179,0.0096</t>
-  </si>
-  <si>
-    <t>0.2563,0.0034,0.8749,0.0037</t>
-  </si>
-  <si>
-    <t>0.0244,0.0077,0.9709,0.0064</t>
-  </si>
-  <si>
-    <t>0.7793,0.0089,0.3351,0.0022</t>
-  </si>
-  <si>
-    <t>0.0340,0.9563,0.0201,0.0010</t>
-  </si>
-  <si>
-    <t>0.0896,0.9235,0.0046,0.0009</t>
-  </si>
-  <si>
-    <t>0.3028,0.7908,0.0074,0.0005</t>
-  </si>
-  <si>
-    <t>0.0218,0.9691,0.0129,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.9963,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.7286,0.0104,0.2701,0.0185</t>
-  </si>
-  <si>
-    <t>0.5067,0.0581,0.4235,0.0807</t>
-  </si>
-  <si>
-    <t>0.0209,0.0028,0.9757,0.0073</t>
-  </si>
-  <si>
-    <t>0.0742,0.0191,0.9166,0.0103</t>
-  </si>
-  <si>
-    <t>0.1708,0.0009,0.9367,0.0005</t>
-  </si>
-  <si>
-    <t>0.0987,0.0051,0.8473,0.0551</t>
-  </si>
-  <si>
-    <t>0.0051,0.0013,0.9920,0.0028</t>
-  </si>
-  <si>
-    <t>0.4578,0.5510,0.0522,0.0085</t>
-  </si>
-  <si>
-    <t>0.5631,0.1420,0.3735,0.0077</t>
-  </si>
-  <si>
-    <t>0.0022,0.0131,0.9917,0.0034</t>
-  </si>
-  <si>
-    <t>0.0196,0.9507,0.0487,0.0005</t>
-  </si>
-  <si>
-    <t>0.9001,0.0800,0.0299,0.0080</t>
-  </si>
-  <si>
-    <t>0.2774,0.0695,0.6778,0.0104</t>
-  </si>
-  <si>
-    <t>0.8394,0.2502,0.0059,0.0020</t>
-  </si>
-  <si>
-    <t>0.0131,0.9747,0.0504,0.0001</t>
-  </si>
-  <si>
-    <t>0.0079,0.8533,0.3645,0.0182</t>
-  </si>
-  <si>
-    <t>0.1727,0.1551,0.7671,0.0266</t>
-  </si>
-  <si>
-    <t>0.3625,0.0574,0.6384,0.0128</t>
-  </si>
-  <si>
-    <t>0.6023,0.0031,0.5241,0.0051</t>
-  </si>
-  <si>
-    <t>0.0122,0.3244,0.9162,0.0076</t>
-  </si>
-  <si>
-    <t>0.0191,0.9697,0.0157,0.0001</t>
-  </si>
-  <si>
-    <t>0.2470,0.1072,0.6864,0.0191</t>
-  </si>
-  <si>
-    <t>0.1789,0.4565,0.0473,0.6969</t>
-  </si>
-  <si>
-    <t>0.0057,0.9764,0.0232,0.0044</t>
-  </si>
-  <si>
-    <t>0.0233,0.9446,0.0523,0.0004</t>
-  </si>
-  <si>
-    <t>0.0044,0.9861,0.0524,0.0004</t>
-  </si>
-  <si>
-    <t>0.0159,0.1534,0.9426,0.0128</t>
-  </si>
-  <si>
-    <t>0.0018,0.1805,0.9887,0.0004</t>
-  </si>
-  <si>
-    <t>0.2491,0.0407,0.7791,0.0128</t>
-  </si>
-  <si>
-    <t>0.0485,0.0070,0.9517,0.0090</t>
-  </si>
-  <si>
-    <t>0.0357,0.0479,0.9258,0.0327</t>
-  </si>
-  <si>
-    <t>0.0095,0.1552,0.9526,0.0023</t>
-  </si>
-  <si>
-    <t>0.9752,0.0592,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9924,0.0037,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9841,0.0077,0.0041,0.0010</t>
-  </si>
-  <si>
-    <t>0.0223,0.0524,0.9677,0.0037</t>
-  </si>
-  <si>
-    <t>0.9953,0.0035,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9837,0.0106,0.0030,0.0006</t>
-  </si>
-  <si>
-    <t>0.0071,0.7703,0.9103,0.0022</t>
-  </si>
-  <si>
-    <t>0.0226,0.0670,0.9536,0.0030</t>
-  </si>
-  <si>
-    <t>0.0527,0.4325,0.7008,0.0205</t>
-  </si>
-  <si>
-    <t>0.0006,0.8009,0.9729,0.0002</t>
-  </si>
-  <si>
-    <t>0.0127,0.0346,0.9566,0.0209</t>
-  </si>
-  <si>
-    <t>0.0187,0.9638,0.0110,0.0003</t>
-  </si>
-  <si>
-    <t>0.0090,0.9829,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.6945,0.0303,0.4037,0.0063</t>
-  </si>
-  <si>
-    <t>0.7291,0.1569,0.1397,0.0061</t>
-  </si>
-  <si>
-    <t>0.0044,0.0290,0.9806,0.0024</t>
-  </si>
-  <si>
-    <t>0.0012,0.8751,0.9079,0.0002</t>
-  </si>
-  <si>
-    <t>0.0049,0.6761,0.8526,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.9971,0.1774,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.9351,0.6080,0.0008</t>
-  </si>
-  <si>
-    <t>0.0127,0.0013,0.2173,0.8959</t>
-  </si>
-  <si>
-    <t>0.0079,0.0026,0.0008,0.9958</t>
-  </si>
-  <si>
-    <t>0.0147,0.0006,0.0006,0.9956</t>
-  </si>
-  <si>
-    <t>0.0080,0.0019,0.0010,0.9958</t>
-  </si>
-  <si>
-    <t>0.0285,0.0032,0.0064,0.9818</t>
-  </si>
-  <si>
-    <t>0.0142,0.0025,0.0008,0.9949</t>
-  </si>
-  <si>
-    <t>0.0003,0.9720,0.8626,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.8311,0.9031,0.0011</t>
-  </si>
-  <si>
-    <t>0.0086,0.7511,0.7936,0.0031</t>
-  </si>
-  <si>
-    <t>0.0387,0.0247,0.9611,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.8879,0.8643,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.5859,0.9435,0.0020</t>
-  </si>
-  <si>
-    <t>0.9935,0.0012,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9954,0.0025,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0019,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9949,0.0033,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9216,0.1269,0.0015,0.0016</t>
-  </si>
-  <si>
-    <t>0.9967,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0013,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0012,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0020,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.0011,0.9934,0.0083</t>
-  </si>
-  <si>
-    <t>0.5104,0.0552,0.4553,0.0304</t>
-  </si>
-  <si>
-    <t>0.7044,0.0012,0.2089,0.0187</t>
-  </si>
-  <si>
-    <t>0.3861,0.0198,0.7180,0.0107</t>
-  </si>
-  <si>
-    <t>0.0213,0.9741,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.0144,0.9730,0.0037,0.0025</t>
-  </si>
-  <si>
-    <t>0.1372,0.9112,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.5078,0.6838,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.0723,0.9379,0.0056,0.0008</t>
-  </si>
-  <si>
-    <t>0.0125,0.9796,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.6251,0.5889,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.7815,0.1535,0.0854,0.0063</t>
-  </si>
-  <si>
-    <t>0.3412,0.0058,0.7642,0.0064</t>
-  </si>
-  <si>
-    <t>0.6864,0.1814,0.1569,0.0154</t>
-  </si>
-  <si>
-    <t>0.5324,0.0228,0.5120,0.0310</t>
-  </si>
-  <si>
-    <t>0.4930,0.0982,0.0758,0.3556</t>
-  </si>
-  <si>
-    <t>0.0106,0.9695,0.0544,0.0009</t>
-  </si>
-  <si>
-    <t>0.0060,0.9780,0.0182,0.0012</t>
-  </si>
-  <si>
-    <t>0.0112,0.9703,0.0254,0.0057</t>
-  </si>
-  <si>
-    <t>0.0009,0.9720,0.7315,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.9908,0.0293,0.0001</t>
-  </si>
-  <si>
-    <t>0.5446,0.4328,0.0266,0.0003</t>
-  </si>
-  <si>
-    <t>0.8471,0.2369,0.0099,0.0019</t>
-  </si>
-  <si>
-    <t>0.9887,0.0082,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9954,0.0004,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9919,0.0057,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9915,0.0101,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0015,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9875,0.0030,0.0030,0.0016</t>
-  </si>
-  <si>
-    <t>0.0093,0.6111,0.8746,0.0041</t>
-  </si>
-  <si>
-    <t>0.0052,0.4481,0.8985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0522,0.0200,0.9419,0.0011</t>
-  </si>
-  <si>
-    <t>0.0220,0.0331,0.9606,0.0017</t>
-  </si>
-  <si>
-    <t>0.6922,0.0415,0.2018,0.0740</t>
-  </si>
-  <si>
-    <t>0.8274,0.0141,0.1617,0.0092</t>
-  </si>
-  <si>
-    <t>0.4936,0.0049,0.7076,0.0031</t>
-  </si>
-  <si>
-    <t>0.6558,0.0802,0.3173,0.0161</t>
-  </si>
-  <si>
-    <t>0.0512,0.0024,0.0010,0.9864</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.0022,0.9979</t>
-  </si>
-  <si>
-    <t>0.0103,0.0021,0.0020,0.9943</t>
-  </si>
-  <si>
-    <t>0.0366,0.0111,0.0015,0.9853</t>
-  </si>
-  <si>
-    <t>0.0011,0.9555,0.5976,0.0028</t>
-  </si>
-  <si>
-    <t>0.9792,0.0087,0.0011,0.0032</t>
-  </si>
-  <si>
-    <t>0.0196,0.9613,0.0030,0.0106</t>
-  </si>
-  <si>
-    <t>0.9895,0.0003,0.0003,0.0048</t>
-  </si>
-  <si>
-    <t>0.7840,0.3161,0.0130,0.0024</t>
-  </si>
-  <si>
-    <t>0.9671,0.0109,0.0034,0.0067</t>
-  </si>
-  <si>
-    <t>0.6140,0.0130,0.0474,0.4222</t>
-  </si>
-  <si>
-    <t>0.9449,0.0255,0.0046,0.0150</t>
-  </si>
-  <si>
-    <t>0.0025,0.0112,0.9886,0.0062</t>
-  </si>
-  <si>
-    <t>0.8267,0.0011,0.0030,0.2754</t>
-  </si>
-  <si>
-    <t>0.9588,0.0092,0.0043,0.0146</t>
-  </si>
-  <si>
-    <t>0.6731,0.3425,0.0329,0.0300</t>
-  </si>
-  <si>
-    <t>0.9433,0.0136,0.0290,0.0067</t>
-  </si>
-  <si>
-    <t>0.9503,0.0311,0.0106,0.0031</t>
-  </si>
-  <si>
-    <t>0.5104,0.4565,0.0767,0.0566</t>
-  </si>
-  <si>
-    <t>0.5489,0.4464,0.0732,0.0165</t>
-  </si>
-  <si>
-    <t>0.4442,0.5622,0.0263,0.0250</t>
-  </si>
-  <si>
-    <t>0.9943,0.0014,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9721,0.0113,0.0018,0.0052</t>
-  </si>
-  <si>
-    <t>0.9945,0.0038,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0001,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9936,0.0009,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9907,0.0048,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9939,0.0015,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9898,0.0014,0.0003,0.0024</t>
-  </si>
-  <si>
-    <t>0.9171,0.1700,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.6166,0.5297,0.0101,0.0013</t>
-  </si>
-  <si>
-    <t>0.5761,0.5354,0.0122,0.0008</t>
-  </si>
-  <si>
-    <t>0.8872,0.0648,0.0571,0.0105</t>
-  </si>
-  <si>
-    <t>0.9658,0.0645,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.9340,0.0773,0.0147,0.0017</t>
-  </si>
-  <si>
-    <t>0.9763,0.0328,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.8535,0.2491,0.0041,0.0015</t>
-  </si>
-  <si>
-    <t>0.0034,0.0400,0.9874,0.0004</t>
-  </si>
-  <si>
-    <t>0.9727,0.0327,0.0055,0.0003</t>
-  </si>
-  <si>
-    <t>0.0068,0.0025,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0287,0.9931,0.0020</t>
-  </si>
-  <si>
-    <t>0.0407,0.0100,0.9654,0.0021</t>
-  </si>
-  <si>
-    <t>0.0099,0.3559,0.9369,0.0069</t>
-  </si>
-  <si>
-    <t>0.0924,0.0223,0.9156,0.0019</t>
-  </si>
-  <si>
-    <t>0.0863,0.0023,0.9603,0.0004</t>
-  </si>
-  <si>
-    <t>0.0058,0.0025,0.9937,0.0003</t>
-  </si>
-  <si>
-    <t>0.2183,0.0110,0.8687,0.0024</t>
-  </si>
-  <si>
-    <t>0.0945,0.0241,0.9141,0.0203</t>
-  </si>
-  <si>
-    <t>0.7433,0.0865,0.1949,0.0058</t>
-  </si>
-  <si>
-    <t>0.5062,0.0311,0.6182,0.0035</t>
-  </si>
-  <si>
-    <t>0.0740,0.3755,0.6757,0.0033</t>
-  </si>
-  <si>
-    <t>0.6103,0.0482,0.4479,0.0019</t>
-  </si>
-  <si>
-    <t>0.6275,0.0262,0.5022,0.0061</t>
-  </si>
-  <si>
-    <t>0.4229,0.0727,0.6045,0.0120</t>
-  </si>
-  <si>
-    <t>0.9075,0.1477,0.0058,0.0009</t>
-  </si>
-  <si>
-    <t>0.8420,0.3540,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.8804,0.1886,0.0102,0.0011</t>
-  </si>
-  <si>
-    <t>0.9763,0.0208,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.6124,0.5419,0.0068,0.0012</t>
-  </si>
-  <si>
-    <t>0.7946,0.0297,0.1992,0.0044</t>
-  </si>
-  <si>
-    <t>0.9359,0.0060,0.0496,0.0016</t>
-  </si>
-  <si>
-    <t>0.7415,0.0205,0.3160,0.0051</t>
-  </si>
-  <si>
-    <t>0.7872,0.0012,0.3195,0.0018</t>
-  </si>
-  <si>
-    <t>0.6990,0.0070,0.3395,0.0113</t>
-  </si>
-  <si>
-    <t>0.0170,0.0047,0.9756,0.0099</t>
-  </si>
-  <si>
-    <t>0.0877,0.2465,0.7340,0.0443</t>
-  </si>
-  <si>
-    <t>0.0248,0.2330,0.9200,0.0097</t>
-  </si>
-  <si>
-    <t>0.1522,0.0134,0.9091,0.0016</t>
-  </si>
-  <si>
-    <t>0.0107,0.2251,0.9475,0.0020</t>
-  </si>
-  <si>
-    <t>0.9953,0.0008,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9914,0.0087,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0025,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0028,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0021,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0002,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9928,0.0048,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.2418,0.0093,0.8604,0.0028</t>
-  </si>
-  <si>
-    <t>0.8618,0.0598,0.0860,0.0099</t>
-  </si>
-  <si>
-    <t>0.9293,0.0029,0.0316,0.0109</t>
-  </si>
-  <si>
-    <t>0.0121,0.2435,0.9410,0.0026</t>
-  </si>
-  <si>
-    <t>0.0005,0.0142,0.9949,0.0017</t>
-  </si>
-  <si>
-    <t>0.0309,0.0334,0.9520,0.0021</t>
-  </si>
-  <si>
-    <t>0.0015,0.0065,0.9965,0.0008</t>
-  </si>
-  <si>
-    <t>0.0097,0.0400,0.9552,0.0019</t>
-  </si>
-  <si>
-    <t>0.0058,0.0875,0.9766,0.0046</t>
-  </si>
-  <si>
-    <t>0.0223,0.0109,0.9711,0.0009</t>
-  </si>
-  <si>
-    <t>0.2256,0.0536,0.7557,0.0147</t>
-  </si>
-  <si>
-    <t>0.5588,0.0091,0.5611,0.0100</t>
-  </si>
-  <si>
-    <t>0.5495,0.0077,0.4915,0.0168</t>
-  </si>
-  <si>
-    <t>0.8218,0.0028,0.0540,0.0530</t>
-  </si>
-  <si>
-    <t>0.9916,0.0068,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0017,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9938,0.0062,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9905,0.0031,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9967,0.0009,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0027,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0031,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0018,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0248,0.0735,0.9267,0.0018</t>
-  </si>
-  <si>
-    <t>0.0007,0.0443,0.9934,0.0009</t>
-  </si>
-  <si>
-    <t>0.0155,0.4612,0.8697,0.0059</t>
-  </si>
-  <si>
-    <t>0.0829,0.0425,0.8688,0.0101</t>
-  </si>
-  <si>
-    <t>0.0027,0.0049,0.9928,0.0026</t>
-  </si>
-  <si>
-    <t>0.2897,0.0081,0.5806,0.0853</t>
-  </si>
-  <si>
-    <t>0.3720,0.0119,0.6916,0.0135</t>
-  </si>
-  <si>
-    <t>0.0547,0.0113,0.8132,0.1172</t>
-  </si>
-  <si>
-    <t>0.7739,0.0012,0.0072,0.2978</t>
-  </si>
-  <si>
-    <t>0.0444,0.0264,0.0055,0.9760</t>
-  </si>
-  <si>
-    <t>0.0033,0.0009,0.0015,0.9972</t>
-  </si>
-  <si>
-    <t>0.0027,0.0002,0.0004,0.9985</t>
-  </si>
-  <si>
-    <t>0.0031,0.0013,0.0004,0.9980</t>
-  </si>
-  <si>
-    <t>0.9074,0.0121,0.0213,0.0430</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.7056,0.0581,0.1481,0.0911</t>
+  </si>
+  <si>
+    <t>0.0654,0.0126,0.0059,0.9686</t>
+  </si>
+  <si>
+    <t>0.5401,0.0202,0.0119,0.5492</t>
+  </si>
+  <si>
+    <t>0.1159,0.0248,0.0032,0.9490</t>
+  </si>
+  <si>
+    <t>0.9967,0.0020,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9888,0.0077,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0016,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0098,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.7177,0.0136,0.2213,0.0380</t>
+  </si>
+  <si>
+    <t>0.6168,0.0096,0.4908,0.0093</t>
+  </si>
+  <si>
+    <t>0.1380,0.0157,0.9027,0.0007</t>
+  </si>
+  <si>
+    <t>0.1014,0.0090,0.9173,0.0043</t>
+  </si>
+  <si>
+    <t>0.8788,0.0141,0.1106,0.0051</t>
+  </si>
+  <si>
+    <t>0.0029,0.9932,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.0126,0.9794,0.0205,0.0002</t>
+  </si>
+  <si>
+    <t>0.2620,0.8176,0.0084,0.0009</t>
+  </si>
+  <si>
+    <t>0.0100,0.9845,0.0095,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.9932,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.5675,0.0050,0.6203,0.0026</t>
+  </si>
+  <si>
+    <t>0.5662,0.0137,0.4242,0.0267</t>
+  </si>
+  <si>
+    <t>0.0034,0.0078,0.9894,0.0031</t>
+  </si>
+  <si>
+    <t>0.3057,0.0272,0.4808,0.1886</t>
+  </si>
+  <si>
+    <t>0.0177,0.0027,0.9816,0.0049</t>
+  </si>
+  <si>
+    <t>0.0731,0.0040,0.8875,0.0401</t>
+  </si>
+  <si>
+    <t>0.0255,0.0012,0.9816,0.0015</t>
+  </si>
+  <si>
+    <t>0.5532,0.5097,0.0321,0.0014</t>
+  </si>
+  <si>
+    <t>0.5059,0.2590,0.3253,0.0296</t>
+  </si>
+  <si>
+    <t>0.0012,0.0037,0.9960,0.0020</t>
+  </si>
+  <si>
+    <t>0.0132,0.9626,0.0442,0.0006</t>
+  </si>
+  <si>
+    <t>0.9322,0.0192,0.0259,0.0106</t>
+  </si>
+  <si>
+    <t>0.4708,0.0831,0.4632,0.0035</t>
+  </si>
+  <si>
+    <t>0.5369,0.6063,0.0088,0.0027</t>
+  </si>
+  <si>
+    <t>0.0148,0.9643,0.0872,0.0004</t>
+  </si>
+  <si>
+    <t>0.0183,0.9030,0.1479,0.0036</t>
+  </si>
+  <si>
+    <t>0.0379,0.0196,0.9514,0.0106</t>
+  </si>
+  <si>
+    <t>0.0504,0.1670,0.8363,0.0036</t>
+  </si>
+  <si>
+    <t>0.2938,0.0063,0.6496,0.0506</t>
+  </si>
+  <si>
+    <t>0.0167,0.4946,0.8118,0.0019</t>
+  </si>
+  <si>
+    <t>0.0094,0.9565,0.1230,0.0022</t>
+  </si>
+  <si>
+    <t>0.0108,0.0086,0.9849,0.0004</t>
+  </si>
+  <si>
+    <t>0.1274,0.5963,0.0331,0.6072</t>
+  </si>
+  <si>
+    <t>0.0070,0.9519,0.0283,0.0589</t>
+  </si>
+  <si>
+    <t>0.0096,0.9651,0.0495,0.0012</t>
+  </si>
+  <si>
+    <t>0.0117,0.9628,0.1524,0.0019</t>
+  </si>
+  <si>
+    <t>0.0055,0.0532,0.9855,0.0024</t>
+  </si>
+  <si>
+    <t>0.0038,0.0577,0.9888,0.0007</t>
+  </si>
+  <si>
+    <t>0.0512,0.0057,0.9573,0.0048</t>
+  </si>
+  <si>
+    <t>0.0272,0.0114,0.9694,0.0034</t>
+  </si>
+  <si>
+    <t>0.0014,0.0164,0.9917,0.0020</t>
+  </si>
+  <si>
+    <t>0.0133,0.0237,0.9677,0.0065</t>
+  </si>
+  <si>
+    <t>0.9876,0.0137,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9917,0.0049,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9698,0.0039,0.0185,0.0023</t>
+  </si>
+  <si>
+    <t>0.0158,0.0498,0.9776,0.0009</t>
+  </si>
+  <si>
+    <t>0.9924,0.0033,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9912,0.0054,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9856,0.0184,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0041,0.8006,0.9225,0.0010</t>
+  </si>
+  <si>
+    <t>0.0140,0.0390,0.9693,0.0043</t>
+  </si>
+  <si>
+    <t>0.0035,0.0056,0.9840,0.0105</t>
+  </si>
+  <si>
+    <t>0.0022,0.7918,0.9221,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.9983,0.0006</t>
+  </si>
+  <si>
+    <t>0.0216,0.9633,0.0163,0.0019</t>
+  </si>
+  <si>
+    <t>0.0064,0.9886,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.8075,0.0237,0.2231,0.0064</t>
+  </si>
+  <si>
+    <t>0.8526,0.1252,0.0531,0.0032</t>
+  </si>
+  <si>
+    <t>0.0006,0.0064,0.9970,0.0011</t>
+  </si>
+  <si>
+    <t>0.0042,0.2914,0.9654,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.9253,0.6794,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.9888,0.0383,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.9458,0.8476,0.0006</t>
+  </si>
+  <si>
+    <t>0.0309,0.0125,0.0024,0.9821</t>
+  </si>
+  <si>
+    <t>0.0206,0.0023,0.0014,0.9917</t>
+  </si>
+  <si>
+    <t>0.0014,0.0188,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.0332,0.0010,0.0257,0.9654</t>
+  </si>
+  <si>
+    <t>0.1217,0.0030,0.0047,0.9584</t>
+  </si>
+  <si>
+    <t>0.0172,0.0020,0.0021,0.9921</t>
+  </si>
+  <si>
+    <t>0.0005,0.9903,0.3768,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.8548,0.9209,0.0005</t>
+  </si>
+  <si>
+    <t>0.0384,0.1992,0.8698,0.0017</t>
+  </si>
+  <si>
+    <t>0.0076,0.5263,0.9177,0.0027</t>
+  </si>
+  <si>
+    <t>0.0004,0.9915,0.3629,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9796,0.2742,0.0002</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0013,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0100,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0039,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0019,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0021,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9889,0.0095,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0016,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0007,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.0051,0.0030,0.9880,0.0084</t>
+  </si>
+  <si>
+    <t>0.0765,0.0383,0.8785,0.0439</t>
+  </si>
+  <si>
+    <t>0.7418,0.0077,0.0776,0.0978</t>
+  </si>
+  <si>
+    <t>0.3547,0.0040,0.7808,0.0046</t>
+  </si>
+  <si>
+    <t>0.0680,0.9272,0.0112,0.0011</t>
+  </si>
+  <si>
+    <t>0.0054,0.9911,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.0332,0.9700,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.6283,0.6575,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0249,0.9673,0.0043,0.0010</t>
+  </si>
+  <si>
+    <t>0.0043,0.9888,0.0070,0.0004</t>
+  </si>
+  <si>
+    <t>0.5803,0.6170,0.0040,0.0005</t>
+  </si>
+  <si>
+    <t>0.7514,0.0524,0.2334,0.0064</t>
+  </si>
+  <si>
+    <t>0.1567,0.0109,0.8940,0.0042</t>
+  </si>
+  <si>
+    <t>0.7943,0.0912,0.1033,0.0063</t>
+  </si>
+  <si>
+    <t>0.4778,0.0617,0.5858,0.0067</t>
+  </si>
+  <si>
+    <t>0.1408,0.0570,0.0050,0.8841</t>
+  </si>
+  <si>
+    <t>0.0030,0.9877,0.0261,0.0013</t>
+  </si>
+  <si>
+    <t>0.0227,0.9437,0.0718,0.0027</t>
+  </si>
+  <si>
+    <t>0.0051,0.9893,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.0022,0.9783,0.4465,0.0003</t>
+  </si>
+  <si>
+    <t>0.0210,0.9645,0.0229,0.0001</t>
+  </si>
+  <si>
+    <t>0.6205,0.4311,0.0305,0.0013</t>
+  </si>
+  <si>
+    <t>0.8851,0.1747,0.0098,0.0007</t>
+  </si>
+  <si>
+    <t>0.9960,0.0019,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9875,0.0039,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.9861,0.0014,0.0022,0.0031</t>
+  </si>
+  <si>
+    <t>0.9977,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9903,0.0073,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.9762,0.0042,0.0226,0.0010</t>
+  </si>
+  <si>
+    <t>0.9819,0.0042,0.0042,0.0020</t>
+  </si>
+  <si>
+    <t>0.0046,0.4289,0.9244,0.0007</t>
+  </si>
+  <si>
+    <t>0.0255,0.3983,0.8125,0.0045</t>
+  </si>
+  <si>
+    <t>0.0224,0.0379,0.9583,0.0008</t>
+  </si>
+  <si>
+    <t>0.0206,0.0481,0.9459,0.0002</t>
+  </si>
+  <si>
+    <t>0.8282,0.0547,0.0629,0.0173</t>
+  </si>
+  <si>
+    <t>0.5839,0.0202,0.4812,0.0073</t>
+  </si>
+  <si>
+    <t>0.4405,0.0075,0.7060,0.0061</t>
+  </si>
+  <si>
+    <t>0.7587,0.1084,0.1559,0.0127</t>
+  </si>
+  <si>
+    <t>0.1591,0.0032,0.0073,0.9320</t>
+  </si>
+  <si>
+    <t>0.0006,0.0026,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.0113,0.0166,0.0007,0.9936</t>
+  </si>
+  <si>
+    <t>0.0324,0.0068,0.0024,0.9867</t>
+  </si>
+  <si>
+    <t>0.0043,0.8178,0.8553,0.0019</t>
+  </si>
+  <si>
+    <t>0.9815,0.0026,0.0005,0.0063</t>
+  </si>
+  <si>
+    <t>0.1877,0.8403,0.0095,0.0061</t>
+  </si>
+  <si>
+    <t>0.9305,0.0030,0.0007,0.0684</t>
+  </si>
+  <si>
+    <t>0.9095,0.0889,0.0148,0.0073</t>
+  </si>
+  <si>
+    <t>0.9760,0.0065,0.0055,0.0024</t>
+  </si>
+  <si>
+    <t>0.6056,0.0499,0.1575,0.3329</t>
+  </si>
+  <si>
+    <t>0.9774,0.0029,0.0018,0.0076</t>
+  </si>
+  <si>
+    <t>0.0012,0.0139,0.9530,0.1016</t>
+  </si>
+  <si>
+    <t>0.2981,0.0032,0.0135,0.8471</t>
+  </si>
+  <si>
+    <t>0.8511,0.0038,0.0092,0.1712</t>
+  </si>
+  <si>
+    <t>0.3512,0.6068,0.0465,0.0382</t>
+  </si>
+  <si>
+    <t>0.9048,0.0520,0.0097,0.0117</t>
+  </si>
+  <si>
+    <t>0.8943,0.0224,0.0926,0.0069</t>
+  </si>
+  <si>
+    <t>0.7345,0.2353,0.0748,0.0072</t>
+  </si>
+  <si>
+    <t>0.8873,0.1290,0.0130,0.0037</t>
+  </si>
+  <si>
+    <t>0.8154,0.1840,0.0307,0.0046</t>
+  </si>
+  <si>
+    <t>0.9938,0.0018,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9844,0.0055,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.9965,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9857,0.0003,0.0003,0.0110</t>
+  </si>
+  <si>
+    <t>0.9790,0.0071,0.0006,0.0043</t>
+  </si>
+  <si>
+    <t>0.9881,0.0079,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9756,0.0231,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.4128,0.7310,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.8146,0.2855,0.0080,0.0009</t>
+  </si>
+  <si>
+    <t>0.8817,0.2347,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.8034,0.1760,0.0656,0.0118</t>
+  </si>
+  <si>
+    <t>0.9944,0.0017,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9824,0.0292,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9858,0.0160,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.9367,0.0937,0.0059,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0350,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.9721,0.0277,0.0074,0.0005</t>
+  </si>
+  <si>
+    <t>0.0048,0.0031,0.9933,0.0010</t>
+  </si>
+  <si>
+    <t>0.0056,0.0110,0.9914,0.0009</t>
+  </si>
+  <si>
+    <t>0.0313,0.0025,0.9777,0.0011</t>
+  </si>
+  <si>
+    <t>0.0043,0.1721,0.9765,0.0012</t>
+  </si>
+  <si>
+    <t>0.0064,0.0069,0.9897,0.0011</t>
+  </si>
+  <si>
+    <t>0.0137,0.0014,0.9902,0.0006</t>
+  </si>
+  <si>
+    <t>0.0099,0.0043,0.9872,0.0021</t>
+  </si>
+  <si>
+    <t>0.1315,0.0519,0.8241,0.0092</t>
+  </si>
+  <si>
+    <t>0.2392,0.0062,0.8911,0.0009</t>
+  </si>
+  <si>
+    <t>0.6806,0.0233,0.4209,0.0051</t>
+  </si>
+  <si>
+    <t>0.0790,0.2665,0.6603,0.0013</t>
+  </si>
+  <si>
+    <t>0.2221,0.2319,0.4574,0.0021</t>
+  </si>
+  <si>
+    <t>0.8137,0.0891,0.1189,0.0047</t>
+  </si>
+  <si>
+    <t>0.5809,0.0543,0.5160,0.0091</t>
+  </si>
+  <si>
+    <t>0.4518,0.0463,0.5630,0.0348</t>
+  </si>
+  <si>
+    <t>0.7115,0.4025,0.0153,0.0018</t>
+  </si>
+  <si>
+    <t>0.0706,0.9540,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.8106,0.3071,0.0088,0.0012</t>
+  </si>
+  <si>
+    <t>0.9890,0.0021,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.8722,0.1782,0.0103,0.0006</t>
+  </si>
+  <si>
+    <t>0.6728,0.0261,0.1187,0.1667</t>
+  </si>
+  <si>
+    <t>0.7740,0.1084,0.1512,0.0094</t>
+  </si>
+  <si>
+    <t>0.7523,0.0175,0.1630,0.0417</t>
+  </si>
+  <si>
+    <t>0.8631,0.0089,0.1428,0.0033</t>
+  </si>
+  <si>
+    <t>0.9196,0.0128,0.0366,0.0085</t>
+  </si>
+  <si>
+    <t>0.0241,0.0222,0.9532,0.0134</t>
+  </si>
+  <si>
+    <t>0.0649,0.2769,0.8142,0.0152</t>
+  </si>
+  <si>
+    <t>0.0178,0.0810,0.9645,0.0049</t>
+  </si>
+  <si>
+    <t>0.0387,0.0135,0.9545,0.0058</t>
+  </si>
+  <si>
+    <t>0.0900,0.0684,0.8858,0.0053</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9805,0.0371,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9941,0.0037,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0027,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9922,0.0063,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0049,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0011,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0149,0.0110,0.9816,0.0017</t>
+  </si>
+  <si>
+    <t>0.3566,0.3583,0.2011,0.0029</t>
+  </si>
+  <si>
+    <t>0.9485,0.0191,0.0317,0.0014</t>
+  </si>
+  <si>
+    <t>0.0040,0.3368,0.9567,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.0262,0.9822,0.0071</t>
+  </si>
+  <si>
+    <t>0.0031,0.0418,0.9804,0.0041</t>
+  </si>
+  <si>
+    <t>0.0039,0.0026,0.9945,0.0013</t>
+  </si>
+  <si>
+    <t>0.0261,0.0667,0.8972,0.0053</t>
+  </si>
+  <si>
+    <t>0.0010,0.0088,0.9949,0.0020</t>
+  </si>
+  <si>
+    <t>0.0079,0.0145,0.9797,0.0032</t>
+  </si>
+  <si>
+    <t>0.1647,0.0489,0.8246,0.0049</t>
+  </si>
+  <si>
+    <t>0.6791,0.0047,0.5100,0.0014</t>
+  </si>
+  <si>
+    <t>0.3782,0.0031,0.6403,0.0187</t>
+  </si>
+  <si>
+    <t>0.8500,0.0035,0.1549,0.0066</t>
+  </si>
+  <si>
+    <t>0.9961,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9892,0.0146,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0029,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9874,0.0216,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9870,0.0083,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0015,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0044,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0605,0.9781,0.0014</t>
+  </si>
+  <si>
+    <t>0.0008,0.1362,0.9908,0.0006</t>
+  </si>
+  <si>
+    <t>0.0062,0.0169,0.9891,0.0008</t>
+  </si>
+  <si>
+    <t>0.0151,0.1428,0.8752,0.0091</t>
+  </si>
+  <si>
+    <t>0.0010,0.0067,0.9948,0.0008</t>
+  </si>
+  <si>
+    <t>0.1165,0.0135,0.7371,0.1670</t>
+  </si>
+  <si>
+    <t>0.2111,0.0094,0.5348,0.2332</t>
+  </si>
+  <si>
+    <t>0.0123,0.0193,0.9009,0.1187</t>
+  </si>
+  <si>
+    <t>0.7468,0.0012,0.0021,0.4560</t>
+  </si>
+  <si>
+    <t>0.0062,0.0524,0.0092,0.9845</t>
+  </si>
+  <si>
+    <t>0.0233,0.0008,0.0031,0.9884</t>
+  </si>
+  <si>
+    <t>0.0016,0.0006,0.0020,0.9972</t>
+  </si>
+  <si>
+    <t>0.0008,0.0021,0.0002,0.9992</t>
+  </si>
+  <si>
+    <t>0.9282,0.0187,0.0124,0.0191</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1996,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2150,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2293,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2318,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2391,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2444,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2489,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2937,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2962,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3102,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3158,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3172,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3424,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3508,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3550,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3609,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3676,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4138,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4166,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4236,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4631,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4645,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4684,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4768,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5188,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5202,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5457,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
